--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/110.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/110.xlsx
@@ -426,13 +426,13 @@
         <v>-19.13177041142403</v>
       </c>
       <c r="E2">
-        <v>-19.73042283614634</v>
+        <v>-12.24658937469612</v>
       </c>
       <c r="F2">
-        <v>-3.999385304087813</v>
+        <v>-1.67204483918506</v>
       </c>
       <c r="G2">
-        <v>-15.20039931920647</v>
+        <v>-13.65396131108479</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.77041842067478</v>
       </c>
       <c r="E3">
-        <v>-19.63844997135801</v>
+        <v>-12.45551667039162</v>
       </c>
       <c r="F3">
-        <v>-3.763568156961058</v>
+        <v>-1.792832403656867</v>
       </c>
       <c r="G3">
-        <v>-14.82579402080599</v>
+        <v>-13.5321583275587</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.34790634267853</v>
       </c>
       <c r="E4">
-        <v>-20.52946331614142</v>
+        <v>-13.79388901981761</v>
       </c>
       <c r="F4">
-        <v>-3.716213706012622</v>
+        <v>-1.653089307906798</v>
       </c>
       <c r="G4">
-        <v>-14.058143734958</v>
+        <v>-13.4147923044652</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.90225787784084</v>
       </c>
       <c r="E5">
-        <v>-20.95026253436173</v>
+        <v>-14.40224726146717</v>
       </c>
       <c r="F5">
-        <v>-3.728138054775921</v>
+        <v>-1.810038422980415</v>
       </c>
       <c r="G5">
-        <v>-15.24338783964374</v>
+        <v>-13.12232886313492</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.45291189703511</v>
       </c>
       <c r="E6">
-        <v>-21.93644671665359</v>
+        <v>-15.46244582277881</v>
       </c>
       <c r="F6">
-        <v>-3.29897664236615</v>
+        <v>-1.596076093041719</v>
       </c>
       <c r="G6">
-        <v>-14.41597108324369</v>
+        <v>-12.8596070241866</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.02281293927868</v>
       </c>
       <c r="E7">
-        <v>-21.15305553693045</v>
+        <v>-15.9154615012458</v>
       </c>
       <c r="F7">
-        <v>-3.241465578691989</v>
+        <v>-1.676296020696227</v>
       </c>
       <c r="G7">
-        <v>-14.55719409041078</v>
+        <v>-12.70275218378021</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.6444208472021</v>
       </c>
       <c r="E8">
-        <v>-23.93414136389612</v>
+        <v>-16.2838181200675</v>
       </c>
       <c r="F8">
-        <v>-3.375584059777048</v>
+        <v>-1.266698989605775</v>
       </c>
       <c r="G8">
-        <v>-13.44062431682197</v>
+        <v>-12.13492176207455</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.33790591193129</v>
       </c>
       <c r="E9">
-        <v>-24.00050137444423</v>
+        <v>-16.68887251415537</v>
       </c>
       <c r="F9">
-        <v>-2.774398073930113</v>
+        <v>-1.26976312062873</v>
       </c>
       <c r="G9">
-        <v>-14.07611218460633</v>
+        <v>-11.59758744793768</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.12670405922007</v>
       </c>
       <c r="E10">
-        <v>-23.62140455113653</v>
+        <v>-18.02427947069544</v>
       </c>
       <c r="F10">
-        <v>-3.731073788851442</v>
+        <v>-1.180427838073817</v>
       </c>
       <c r="G10">
-        <v>-13.42772332242498</v>
+        <v>-11.10921634323485</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.01456682940158</v>
       </c>
       <c r="E11">
-        <v>-23.22952414337101</v>
+        <v>-18.18237976619769</v>
       </c>
       <c r="F11">
-        <v>-3.310789161530071</v>
+        <v>-1.005333335041877</v>
       </c>
       <c r="G11">
-        <v>-12.53920600498681</v>
+        <v>-10.43786728774696</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.00275409018926</v>
       </c>
       <c r="E12">
-        <v>-25.78057605468839</v>
+        <v>-19.61734750461655</v>
       </c>
       <c r="F12">
-        <v>-2.927548296094491</v>
+        <v>-0.2466755342901585</v>
       </c>
       <c r="G12">
-        <v>-13.68057001995742</v>
+        <v>-9.632355983838636</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.07070513091115</v>
       </c>
       <c r="E13">
-        <v>-25.27485197129799</v>
+        <v>-19.98646416111069</v>
       </c>
       <c r="F13">
-        <v>-1.912488418256449</v>
+        <v>-0.411731881134974</v>
       </c>
       <c r="G13">
-        <v>-11.93427820801372</v>
+        <v>-9.401921223248614</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-16.19397613234608</v>
       </c>
       <c r="E14">
-        <v>-26.43451994383927</v>
+        <v>-21.17329828892767</v>
       </c>
       <c r="F14">
-        <v>-2.43258800414555</v>
+        <v>-0.3613000452851373</v>
       </c>
       <c r="G14">
-        <v>-11.81634956946084</v>
+        <v>-9.459879753171329</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-16.33360334485063</v>
       </c>
       <c r="E15">
-        <v>-29.23228299087978</v>
+        <v>-22.1710865436611</v>
       </c>
       <c r="F15">
-        <v>-1.731639246877261</v>
+        <v>-0.2342591352895967</v>
       </c>
       <c r="G15">
-        <v>-11.78211879175446</v>
+        <v>-8.836856885437236</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-16.44734043346505</v>
       </c>
       <c r="E16">
-        <v>-28.5260065624304</v>
+        <v>-23.02336288641784</v>
       </c>
       <c r="F16">
-        <v>-1.668768646106987</v>
+        <v>0.4412115257707873</v>
       </c>
       <c r="G16">
-        <v>-11.60926008700455</v>
+        <v>-8.395343424655703</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-16.49337365189001</v>
       </c>
       <c r="E17">
-        <v>-29.67748440223911</v>
+        <v>-24.30834985747449</v>
       </c>
       <c r="F17">
-        <v>-1.725974042209516</v>
+        <v>0.6112480174412335</v>
       </c>
       <c r="G17">
-        <v>-11.18553232374998</v>
+        <v>-8.127608956092445</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-16.43326878031056</v>
       </c>
       <c r="E18">
-        <v>-29.02314388140671</v>
+        <v>-24.45340491620545</v>
       </c>
       <c r="F18">
-        <v>-1.289841918105187</v>
+        <v>1.034689552934674</v>
       </c>
       <c r="G18">
-        <v>-10.19683290411701</v>
+        <v>-8.360235436766708</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-16.24419409824551</v>
       </c>
       <c r="E19">
-        <v>-32.30625951028934</v>
+        <v>-25.78073387671873</v>
       </c>
       <c r="F19">
-        <v>-1.503491125165624</v>
+        <v>1.301157122332413</v>
       </c>
       <c r="G19">
-        <v>-10.00157792689224</v>
+        <v>-7.794866947210465</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-15.91190027656076</v>
       </c>
       <c r="E20">
-        <v>-29.81522773243271</v>
+        <v>-26.80937218517299</v>
       </c>
       <c r="F20">
-        <v>-0.5227455386211498</v>
+        <v>1.647603564470445</v>
       </c>
       <c r="G20">
-        <v>-10.93454186562183</v>
+        <v>-7.795986956640053</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-15.44333782249783</v>
       </c>
       <c r="E21">
-        <v>-31.81864965809218</v>
+        <v>-27.59742326800258</v>
       </c>
       <c r="F21">
-        <v>-0.3780446639653265</v>
+        <v>2.154430219464488</v>
       </c>
       <c r="G21">
-        <v>-10.63121772679251</v>
+        <v>-7.419199075761401</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-14.84843153985299</v>
       </c>
       <c r="E22">
-        <v>-31.73906374608015</v>
+        <v>-28.46252057411907</v>
       </c>
       <c r="F22">
-        <v>-0.6664250362693213</v>
+        <v>2.536294338276616</v>
       </c>
       <c r="G22">
-        <v>-10.60486617626211</v>
+        <v>-8.25146529023945</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-14.15590409128751</v>
       </c>
       <c r="E23">
-        <v>-33.88783976168597</v>
+        <v>-27.9446234283356</v>
       </c>
       <c r="F23">
-        <v>-0.6148086350334813</v>
+        <v>2.747817954581469</v>
       </c>
       <c r="G23">
-        <v>-10.44158759878929</v>
+        <v>-7.967309238198089</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-13.39169785138902</v>
       </c>
       <c r="E24">
-        <v>-32.90420772775322</v>
+        <v>-28.34867482188853</v>
       </c>
       <c r="F24">
-        <v>0.08230312442503993</v>
+        <v>2.275292337002548</v>
       </c>
       <c r="G24">
-        <v>-9.237591821077874</v>
+        <v>-8.322720342364706</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-12.60054728911843</v>
       </c>
       <c r="E25">
-        <v>-34.32180258320032</v>
+        <v>-28.09420548741063</v>
       </c>
       <c r="F25">
-        <v>-0.5185026407840106</v>
+        <v>2.671853350275144</v>
       </c>
       <c r="G25">
-        <v>-11.04432628642273</v>
+        <v>-7.98766782451959</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-11.81724675042231</v>
       </c>
       <c r="E26">
-        <v>-33.89355250386327</v>
+        <v>-29.84260777809164</v>
       </c>
       <c r="F26">
-        <v>-0.209013810321879</v>
+        <v>2.255489385871222</v>
       </c>
       <c r="G26">
-        <v>-10.40514552041424</v>
+        <v>-7.636435217071051</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-11.0888971465683</v>
       </c>
       <c r="E27">
-        <v>-34.39803893027887</v>
+        <v>-29.01153150254249</v>
       </c>
       <c r="F27">
-        <v>-0.5195405851397185</v>
+        <v>2.510033434873066</v>
       </c>
       <c r="G27">
-        <v>-10.03057024557656</v>
+        <v>-7.83666496811419</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.4420281277621</v>
       </c>
       <c r="E28">
-        <v>-33.75394645839049</v>
+        <v>-28.19983826424631</v>
       </c>
       <c r="F28">
-        <v>-0.7595086813219016</v>
+        <v>2.130284966407689</v>
       </c>
       <c r="G28">
-        <v>-9.787656125841011</v>
+        <v>-7.953245157085762</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.90851237962341</v>
       </c>
       <c r="E29">
-        <v>-32.9358448150201</v>
+        <v>-29.44290895000713</v>
       </c>
       <c r="F29">
-        <v>-0.2922837867534937</v>
+        <v>1.973788139936</v>
       </c>
       <c r="G29">
-        <v>-9.690998528844222</v>
+        <v>-8.132353984386794</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.495750600191782</v>
       </c>
       <c r="E30">
-        <v>-31.84333219299564</v>
+        <v>-29.35076580355449</v>
       </c>
       <c r="F30">
-        <v>-0.5562090965920414</v>
+        <v>1.753352947111829</v>
       </c>
       <c r="G30">
-        <v>-10.59514245803251</v>
+        <v>-7.467414306870082</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.213346377964616</v>
       </c>
       <c r="E31">
-        <v>-31.77883697433237</v>
+        <v>-29.65093084563382</v>
       </c>
       <c r="F31">
-        <v>-0.7368503477531267</v>
+        <v>1.879047760077821</v>
       </c>
       <c r="G31">
-        <v>-9.646044117729843</v>
+        <v>-7.872199812743832</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.049245232706159</v>
       </c>
       <c r="E32">
-        <v>-32.87693774219439</v>
+        <v>-28.01423125013973</v>
       </c>
       <c r="F32">
-        <v>-1.277678171162479</v>
+        <v>1.452955448895422</v>
       </c>
       <c r="G32">
-        <v>-10.78627376417561</v>
+        <v>-8.281217335599777</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.994855678243328</v>
       </c>
       <c r="E33">
-        <v>-33.30251523004391</v>
+        <v>-28.05390895453148</v>
       </c>
       <c r="F33">
-        <v>-0.218438146263529</v>
+        <v>1.843926638933927</v>
       </c>
       <c r="G33">
-        <v>-11.19392325686582</v>
+        <v>-8.181379851691014</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.035072445542164</v>
       </c>
       <c r="E34">
-        <v>-33.13085885277742</v>
+        <v>-28.20386480262573</v>
       </c>
       <c r="F34">
-        <v>-0.01124689147531664</v>
+        <v>2.066227315149203</v>
       </c>
       <c r="G34">
-        <v>-10.18664969483938</v>
+        <v>-8.027753196971544</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.157558524470783</v>
       </c>
       <c r="E35">
-        <v>-32.65007065018129</v>
+        <v>-27.05556209287485</v>
       </c>
       <c r="F35">
-        <v>-0.5188455848887696</v>
+        <v>1.770238388250495</v>
       </c>
       <c r="G35">
-        <v>-11.40842986470546</v>
+        <v>-8.406298108960016</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.350479733374637</v>
       </c>
       <c r="E36">
-        <v>-29.72028532154713</v>
+        <v>-26.08987816168235</v>
       </c>
       <c r="F36">
-        <v>-0.1596265457669725</v>
+        <v>1.795140769113453</v>
       </c>
       <c r="G36">
-        <v>-10.14163784734399</v>
+        <v>-8.412206223969704</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.596567904605717</v>
       </c>
       <c r="E37">
-        <v>-31.6487002506802</v>
+        <v>-26.42030350147438</v>
       </c>
       <c r="F37">
-        <v>-0.2067515389448336</v>
+        <v>2.237117853611935</v>
       </c>
       <c r="G37">
-        <v>-11.01847860959841</v>
+        <v>-8.726584255397793</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.888583478326121</v>
       </c>
       <c r="E38">
-        <v>-31.27319387856281</v>
+        <v>-25.5258845234046</v>
       </c>
       <c r="F38">
-        <v>-0.4247413911959402</v>
+        <v>2.275191276179406</v>
       </c>
       <c r="G38">
-        <v>-10.15962718294906</v>
+        <v>-8.992073483612694</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.21229212902964</v>
       </c>
       <c r="E39">
-        <v>-29.78349512130536</v>
+        <v>-25.18143794217995</v>
       </c>
       <c r="F39">
-        <v>-0.5151692903551455</v>
+        <v>2.062000984660119</v>
       </c>
       <c r="G39">
-        <v>-11.18876703629837</v>
+        <v>-8.614524570685733</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.56745096045723</v>
       </c>
       <c r="E40">
-        <v>-27.81498924325373</v>
+        <v>-25.01326195600367</v>
       </c>
       <c r="F40">
-        <v>0.006857906480269355</v>
+        <v>2.390311150881259</v>
       </c>
       <c r="G40">
-        <v>-10.8856347871965</v>
+        <v>-9.689643552401435</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.94386541789825</v>
       </c>
       <c r="E41">
-        <v>-29.60722037304566</v>
+        <v>-24.88633566470558</v>
       </c>
       <c r="F41">
-        <v>-0.5841399886796351</v>
+        <v>2.572442634999981</v>
       </c>
       <c r="G41">
-        <v>-11.42813576487918</v>
+        <v>-9.404153409874015</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.34526058969231</v>
       </c>
       <c r="E42">
-        <v>-28.4594139720481</v>
+        <v>-23.68867411496478</v>
       </c>
       <c r="F42">
-        <v>0.3620825579857673</v>
+        <v>2.698251762667558</v>
       </c>
       <c r="G42">
-        <v>-10.33741888960387</v>
+        <v>-9.624791351385886</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.7639923476917</v>
       </c>
       <c r="E43">
-        <v>-29.08562894578876</v>
+        <v>-23.30029071113476</v>
       </c>
       <c r="F43">
-        <v>-0.4052507345754707</v>
+        <v>2.559821629250927</v>
       </c>
       <c r="G43">
-        <v>-12.31489605120754</v>
+        <v>-9.730895927685616</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.20259840240147</v>
       </c>
       <c r="E44">
-        <v>-28.67750532853183</v>
+        <v>-22.38670050958957</v>
       </c>
       <c r="F44">
-        <v>0.1194106706008466</v>
+        <v>2.401189271614822</v>
       </c>
       <c r="G44">
-        <v>-11.76505757585153</v>
+        <v>-9.939315584511077</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-12.65148867646197</v>
       </c>
       <c r="E45">
-        <v>-28.63363288070201</v>
+        <v>-22.10319399813413</v>
       </c>
       <c r="F45">
-        <v>-0.5411883104770779</v>
+        <v>2.48140671416712</v>
       </c>
       <c r="G45">
-        <v>-11.45682915330781</v>
+        <v>-10.16074458163405</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-13.10734664698805</v>
       </c>
       <c r="E46">
-        <v>-27.22588528930607</v>
+        <v>-22.145743648157</v>
       </c>
       <c r="F46">
-        <v>-0.5869961994844878</v>
+        <v>2.371573480229934</v>
       </c>
       <c r="G46">
-        <v>-11.87905834916709</v>
+        <v>-10.2393175508482</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-13.55694336779909</v>
       </c>
       <c r="E47">
-        <v>-25.74441819689443</v>
+        <v>-20.76951893071651</v>
       </c>
       <c r="F47">
-        <v>-0.9327534399433902</v>
+        <v>2.672517700932189</v>
       </c>
       <c r="G47">
-        <v>-12.14518329368992</v>
+        <v>-9.99805603243883</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-13.99212721732569</v>
       </c>
       <c r="E48">
-        <v>-26.16593592067393</v>
+        <v>-20.34022639533693</v>
       </c>
       <c r="F48">
-        <v>-0.2607205036046242</v>
+        <v>2.652501031010941</v>
       </c>
       <c r="G48">
-        <v>-10.79228500359665</v>
+        <v>-10.2424896055264</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-14.40220296959498</v>
       </c>
       <c r="E49">
-        <v>-25.25203007506806</v>
+        <v>-19.15700140816123</v>
       </c>
       <c r="F49">
-        <v>-0.5406283341127855</v>
+        <v>2.478893447467027</v>
       </c>
       <c r="G49">
-        <v>-10.08872980283279</v>
+        <v>-10.30329515242573</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-14.78042984542219</v>
       </c>
       <c r="E50">
-        <v>-25.08583101748239</v>
+        <v>-19.74345976649497</v>
       </c>
       <c r="F50">
-        <v>-0.3775227925015628</v>
+        <v>2.35081790658539</v>
       </c>
       <c r="G50">
-        <v>-12.13572848215321</v>
+        <v>-10.53307853224027</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-15.12260382284261</v>
       </c>
       <c r="E51">
-        <v>-25.07396113951604</v>
+        <v>-18.5655093577018</v>
       </c>
       <c r="F51">
-        <v>-0.6818028487348913</v>
+        <v>2.533474575637486</v>
       </c>
       <c r="G51">
-        <v>-11.5279562789481</v>
+        <v>-10.28651459156635</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-15.42558174076435</v>
       </c>
       <c r="E52">
-        <v>-24.79931342781645</v>
+        <v>-18.33036283891266</v>
       </c>
       <c r="F52">
-        <v>-0.4747375057919044</v>
+        <v>2.60882618806574</v>
       </c>
       <c r="G52">
-        <v>-12.20045275668379</v>
+        <v>-10.69926286844299</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-15.69331395059299</v>
       </c>
       <c r="E53">
-        <v>-24.30130185785626</v>
+        <v>-18.18551544074794</v>
       </c>
       <c r="F53">
-        <v>-0.7435187053456628</v>
+        <v>2.311596366797639</v>
       </c>
       <c r="G53">
-        <v>-11.30735097174362</v>
+        <v>-10.53164523345975</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-15.92435417068606</v>
       </c>
       <c r="E54">
-        <v>-24.80351647767717</v>
+        <v>-17.62123107767746</v>
       </c>
       <c r="F54">
-        <v>-1.429000186468879</v>
+        <v>2.502525112734091</v>
       </c>
       <c r="G54">
-        <v>-11.00466254922224</v>
+        <v>-10.29825772073717</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-16.12672632552257</v>
       </c>
       <c r="E55">
-        <v>-23.98150043263314</v>
+        <v>-18.3045257112609</v>
       </c>
       <c r="F55">
-        <v>-0.7257742472102946</v>
+        <v>2.373571502405487</v>
       </c>
       <c r="G55">
-        <v>-11.03739475953332</v>
+        <v>-10.80170718082598</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-16.29800971571235</v>
       </c>
       <c r="E56">
-        <v>-22.16582857812387</v>
+        <v>-16.32314072489097</v>
       </c>
       <c r="F56">
-        <v>-0.774649580710271</v>
+        <v>2.436022120902541</v>
       </c>
       <c r="G56">
-        <v>-11.64719290054113</v>
+        <v>-10.51681489880993</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-16.44493159649055</v>
       </c>
       <c r="E57">
-        <v>-22.64133389591481</v>
+        <v>-16.55980316581368</v>
       </c>
       <c r="F57">
-        <v>-0.8211499848664213</v>
+        <v>2.371619868804491</v>
       </c>
       <c r="G57">
-        <v>-11.4054222869365</v>
+        <v>-10.60535960698983</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-16.56046505326387</v>
       </c>
       <c r="E58">
-        <v>-22.56713677559675</v>
+        <v>-15.70070725006157</v>
       </c>
       <c r="F58">
-        <v>-1.040270558622349</v>
+        <v>2.431466100187144</v>
       </c>
       <c r="G58">
-        <v>-11.99575080015608</v>
+        <v>-11.36259302191928</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-16.64702778200121</v>
       </c>
       <c r="E59">
-        <v>-21.44571572614582</v>
+        <v>-15.79009681740585</v>
       </c>
       <c r="F59">
-        <v>-1.143784177643578</v>
+        <v>2.224037932321731</v>
       </c>
       <c r="G59">
-        <v>-11.64685350374429</v>
+        <v>-11.40463906355916</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-16.69360029703154</v>
       </c>
       <c r="E60">
-        <v>-21.5328127208388</v>
+        <v>-15.19229603894401</v>
       </c>
       <c r="F60">
-        <v>-0.7505507162280278</v>
+        <v>2.760377661142716</v>
       </c>
       <c r="G60">
-        <v>-12.46859189065867</v>
+        <v>-10.99130467452181</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-16.7027565236345</v>
       </c>
       <c r="E61">
-        <v>-21.97718971975015</v>
+        <v>-15.50761614914764</v>
       </c>
       <c r="F61">
-        <v>-0.4307967569104046</v>
+        <v>2.387665345396717</v>
       </c>
       <c r="G61">
-        <v>-12.12544998069799</v>
+        <v>-10.84157194535999</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-16.66587024266145</v>
       </c>
       <c r="E62">
-        <v>-22.01419483265438</v>
+        <v>-15.27954670245601</v>
       </c>
       <c r="F62">
-        <v>-0.7863105086394797</v>
+        <v>2.515278657267592</v>
       </c>
       <c r="G62">
-        <v>-11.2575601562742</v>
+        <v>-11.41638480347458</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-16.58903460516887</v>
       </c>
       <c r="E63">
-        <v>-21.39211438078759</v>
+        <v>-13.74251794894081</v>
       </c>
       <c r="F63">
-        <v>-1.042891513084807</v>
+        <v>2.957958197323648</v>
       </c>
       <c r="G63">
-        <v>-12.33870865262308</v>
+        <v>-11.90914718057967</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-16.4655602806909</v>
       </c>
       <c r="E64">
-        <v>-21.40188273382358</v>
+        <v>-14.32663389608735</v>
       </c>
       <c r="F64">
-        <v>-0.4519888801762244</v>
+        <v>2.268645516962484</v>
       </c>
       <c r="G64">
-        <v>-13.51868166397937</v>
+        <v>-11.74078026189877</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-16.30451079562107</v>
       </c>
       <c r="E65">
-        <v>-22.5410836809561</v>
+        <v>-14.40821542614095</v>
       </c>
       <c r="F65">
-        <v>-0.9894427631539744</v>
+        <v>2.528979854109896</v>
       </c>
       <c r="G65">
-        <v>-12.3503369090319</v>
+        <v>-12.01577782191451</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-16.10295273826356</v>
       </c>
       <c r="E66">
-        <v>-21.88583983666055</v>
+        <v>-14.37836629634941</v>
       </c>
       <c r="F66">
-        <v>-1.279821986000924</v>
+        <v>2.248247798035949</v>
       </c>
       <c r="G66">
-        <v>-12.50005919521536</v>
+        <v>-11.95275444748503</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-15.87357895907266</v>
       </c>
       <c r="E67">
-        <v>-19.71783445262078</v>
+        <v>-13.65687873142284</v>
       </c>
       <c r="F67">
-        <v>-0.8832352933388414</v>
+        <v>2.415949121997904</v>
       </c>
       <c r="G67">
-        <v>-12.7111587813636</v>
+        <v>-11.79168978142548</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-15.61581149219264</v>
       </c>
       <c r="E68">
-        <v>-21.99644816066338</v>
+        <v>-13.84803858907073</v>
       </c>
       <c r="F68">
-        <v>-0.8783371568860879</v>
+        <v>2.374908487393605</v>
       </c>
       <c r="G68">
-        <v>-12.87918238713076</v>
+        <v>-11.98689776524761</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-15.34287234036011</v>
       </c>
       <c r="E69">
-        <v>-21.1857163907889</v>
+        <v>-13.46578117194484</v>
       </c>
       <c r="F69">
-        <v>-0.9818772836642066</v>
+        <v>2.664101488119746</v>
       </c>
       <c r="G69">
-        <v>-12.79524172703729</v>
+        <v>-11.68244447938264</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.05512887006309</v>
       </c>
       <c r="E70">
-        <v>-20.98183109364175</v>
+        <v>-13.90885821571152</v>
       </c>
       <c r="F70">
-        <v>-0.7670451679525716</v>
+        <v>2.544312934735715</v>
       </c>
       <c r="G70">
-        <v>-13.06042941425192</v>
+        <v>-11.45055161793848</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-14.76479207435126</v>
       </c>
       <c r="E71">
-        <v>-21.36099852154197</v>
+        <v>-14.12604209552078</v>
       </c>
       <c r="F71">
-        <v>-0.8164854480212572</v>
+        <v>2.378829978678458</v>
       </c>
       <c r="G71">
-        <v>-13.38170894900661</v>
+        <v>-11.89279217108864</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-14.47342660916628</v>
       </c>
       <c r="E72">
-        <v>-20.19856035704703</v>
+        <v>-13.51266677459082</v>
       </c>
       <c r="F72">
-        <v>-0.7210583515861571</v>
+        <v>2.666220451936107</v>
       </c>
       <c r="G72">
-        <v>-12.69721871061935</v>
+        <v>-11.83453340553794</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-14.19230614465754</v>
       </c>
       <c r="E73">
-        <v>-21.61087648090028</v>
+        <v>-13.53816749212527</v>
       </c>
       <c r="F73">
-        <v>-0.7983417167977397</v>
+        <v>2.618571102192274</v>
       </c>
       <c r="G73">
-        <v>-12.88346661900478</v>
+        <v>-11.91202422111907</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-13.92333555763995</v>
       </c>
       <c r="E74">
-        <v>-21.0181052413528</v>
+        <v>-13.53126900811473</v>
       </c>
       <c r="F74">
-        <v>-1.078722545092899</v>
+        <v>2.421164523165929</v>
       </c>
       <c r="G74">
-        <v>-11.98386146928815</v>
+        <v>-11.8584021379622</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-13.67275244426435</v>
       </c>
       <c r="E75">
-        <v>-19.64075915685461</v>
+        <v>-14.6439143220363</v>
       </c>
       <c r="F75">
-        <v>-1.261353534755509</v>
+        <v>2.433454181953863</v>
       </c>
       <c r="G75">
-        <v>-11.42207622668321</v>
+        <v>-12.02189479649148</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-13.44222695633675</v>
       </c>
       <c r="E76">
-        <v>-21.85061645141468</v>
+        <v>-14.06552150009538</v>
       </c>
       <c r="F76">
-        <v>-1.367794604178232</v>
+        <v>2.58459809826866</v>
       </c>
       <c r="G76">
-        <v>-12.42112985936453</v>
+        <v>-12.13303680447977</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-13.23264855967652</v>
       </c>
       <c r="E77">
-        <v>-22.02637204825878</v>
+        <v>-14.17902461239161</v>
       </c>
       <c r="F77">
-        <v>-1.672232878585495</v>
+        <v>2.218675081756007</v>
       </c>
       <c r="G77">
-        <v>-13.29865333132953</v>
+        <v>-11.9561131704015</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-13.04641670935492</v>
       </c>
       <c r="E78">
-        <v>-22.42996866517164</v>
+        <v>-14.51649379859056</v>
       </c>
       <c r="F78">
-        <v>-1.936600536617137</v>
+        <v>2.331188912608653</v>
       </c>
       <c r="G78">
-        <v>-13.18230288788197</v>
+        <v>-11.47606642482743</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-12.88063183580642</v>
       </c>
       <c r="E79">
-        <v>-22.4515238319475</v>
+        <v>-14.0643710605584</v>
       </c>
       <c r="F79">
-        <v>-0.5369884877448845</v>
+        <v>2.138571953905295</v>
       </c>
       <c r="G79">
-        <v>-12.05195752045815</v>
+        <v>-11.90311113908501</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-12.73818472703042</v>
       </c>
       <c r="E80">
-        <v>-21.71627667790178</v>
+        <v>-14.33121904138996</v>
       </c>
       <c r="F80">
-        <v>-1.046933946010469</v>
+        <v>2.529693906811109</v>
       </c>
       <c r="G80">
-        <v>-11.99404467856578</v>
+        <v>-11.20323969893921</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.61301405105776</v>
       </c>
       <c r="E81">
-        <v>-21.06802268826591</v>
+        <v>-15.11331026596842</v>
       </c>
       <c r="F81">
-        <v>-1.670355798050751</v>
+        <v>2.671687676794584</v>
       </c>
       <c r="G81">
-        <v>-12.13968376020874</v>
+        <v>-11.26023616948009</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.50759561796896</v>
       </c>
       <c r="E82">
-        <v>-23.59137683325802</v>
+        <v>-16.35919059919048</v>
       </c>
       <c r="F82">
-        <v>-0.7281342659408704</v>
+        <v>2.332431463712852</v>
       </c>
       <c r="G82">
-        <v>-12.17263918918237</v>
+        <v>-11.25559557096939</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.41260764765412</v>
       </c>
       <c r="E83">
-        <v>-22.65557525754765</v>
+        <v>-16.83322568017244</v>
       </c>
       <c r="F83">
-        <v>-1.574917932839415</v>
+        <v>2.510333303872879</v>
       </c>
       <c r="G83">
-        <v>-11.66986721731495</v>
+        <v>-11.10448828478034</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-12.32962230654402</v>
       </c>
       <c r="E84">
-        <v>-22.93689717984623</v>
+        <v>-16.78707519593095</v>
       </c>
       <c r="F84">
-        <v>-1.309398015750478</v>
+        <v>2.099415026774962</v>
       </c>
       <c r="G84">
-        <v>-11.65024747171273</v>
+        <v>-10.91491037166895</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-12.24885079464929</v>
       </c>
       <c r="E85">
-        <v>-23.53203574984887</v>
+        <v>-18.87310449484125</v>
       </c>
       <c r="F85">
-        <v>-0.7053044603197161</v>
+        <v>2.061638159737694</v>
       </c>
       <c r="G85">
-        <v>-11.38371264028909</v>
+        <v>-11.17435703152772</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-12.17261391423666</v>
       </c>
       <c r="E86">
-        <v>-24.5401613475698</v>
+        <v>-17.79954089948632</v>
       </c>
       <c r="F86">
-        <v>-1.33139862560143</v>
+        <v>1.999450962074729</v>
       </c>
       <c r="G86">
-        <v>-11.84516305214066</v>
+        <v>-10.9964204285481</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-12.092639537707</v>
       </c>
       <c r="E87">
-        <v>-27.69350365879117</v>
+        <v>-20.31945618550147</v>
       </c>
       <c r="F87">
-        <v>-0.6382207829388037</v>
+        <v>2.052456535445064</v>
       </c>
       <c r="G87">
-        <v>-11.84427800972427</v>
+        <v>-10.7329858563264</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-12.01287099119324</v>
       </c>
       <c r="E88">
-        <v>-27.19178742432923</v>
+        <v>-21.11227515493196</v>
       </c>
       <c r="F88">
-        <v>-1.57128305667593</v>
+        <v>2.031381211983039</v>
       </c>
       <c r="G88">
-        <v>-11.82114811801931</v>
+        <v>-11.2702535964762</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-11.927328297854</v>
       </c>
       <c r="E89">
-        <v>-29.26817504314895</v>
+        <v>-22.81612594773155</v>
       </c>
       <c r="F89">
-        <v>-1.23331744000776</v>
+        <v>1.741692847550024</v>
       </c>
       <c r="G89">
-        <v>-11.19061413809658</v>
+        <v>-10.56945664737284</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-11.84015844837208</v>
       </c>
       <c r="E90">
-        <v>-31.15778444226848</v>
+        <v>-24.55530810927145</v>
       </c>
       <c r="F90">
-        <v>-1.600563359262684</v>
+        <v>1.687192899385038</v>
       </c>
       <c r="G90">
-        <v>-12.26709070699966</v>
+        <v>-10.77465856148975</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-11.74778660680773</v>
       </c>
       <c r="E91">
-        <v>-31.23701940792355</v>
+        <v>-25.31468542111442</v>
       </c>
       <c r="F91">
-        <v>-1.175601769585107</v>
+        <v>1.588481326197838</v>
       </c>
       <c r="G91">
-        <v>-12.74804599169144</v>
+        <v>-10.36549092081982</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-11.65467532611445</v>
       </c>
       <c r="E92">
-        <v>-32.66364749800216</v>
+        <v>-27.42130634177323</v>
       </c>
       <c r="F92">
-        <v>-1.935153378764447</v>
+        <v>1.426603425077564</v>
       </c>
       <c r="G92">
-        <v>-11.34749378057658</v>
+        <v>-10.59896197736931</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-11.56006844761105</v>
       </c>
       <c r="E93">
-        <v>-32.34857035066103</v>
+        <v>-29.44427327992734</v>
       </c>
       <c r="F93">
-        <v>-1.772069374705697</v>
+        <v>1.247096208890912</v>
       </c>
       <c r="G93">
-        <v>-12.23072564559005</v>
+        <v>-10.83193568707419</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-11.46709855116309</v>
       </c>
       <c r="E94">
-        <v>-34.90150366670856</v>
+        <v>-31.72319432560798</v>
       </c>
       <c r="F94">
-        <v>-1.95392004227487</v>
+        <v>1.435410627304129</v>
       </c>
       <c r="G94">
-        <v>-12.11816991940567</v>
+        <v>-10.83518084260094</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-11.37943677240819</v>
       </c>
       <c r="E95">
-        <v>-36.89226245103863</v>
+        <v>-34.06003605642469</v>
       </c>
       <c r="F95">
-        <v>-1.667100314157749</v>
+        <v>0.9773731556001701</v>
       </c>
       <c r="G95">
-        <v>-12.39040139552712</v>
+        <v>-10.73387612023197</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.30428930545393</v>
       </c>
       <c r="E96">
-        <v>-39.36887012596412</v>
+        <v>-36.26533935476708</v>
       </c>
       <c r="F96">
-        <v>-1.779185879063147</v>
+        <v>0.8101224635053388</v>
       </c>
       <c r="G96">
-        <v>-12.69637544011642</v>
+        <v>-11.31601603304153</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-11.2483033094548</v>
       </c>
       <c r="E97">
-        <v>-42.20212444038096</v>
+        <v>-38.08220941074356</v>
       </c>
       <c r="F97">
-        <v>-2.097258252553088</v>
+        <v>0.2725078772514456</v>
       </c>
       <c r="G97">
-        <v>-11.14723531134294</v>
+        <v>-11.08721429319324</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-11.22110335422867</v>
       </c>
       <c r="E98">
-        <v>-43.54860593491868</v>
+        <v>-41.37929021270593</v>
       </c>
       <c r="F98">
-        <v>-2.144968073117325</v>
+        <v>0.3520866485361857</v>
       </c>
       <c r="G98">
-        <v>-13.18785072013809</v>
+        <v>-11.6809863785285</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.22299574954023</v>
       </c>
       <c r="E99">
-        <v>-45.81155061493554</v>
+        <v>-43.29760245529134</v>
       </c>
       <c r="F99">
-        <v>-2.341300259622239</v>
+        <v>-0.1598054731259772</v>
       </c>
       <c r="G99">
-        <v>-12.81447899855691</v>
+        <v>-12.18368524954737</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.2658831349982</v>
       </c>
       <c r="E100">
-        <v>-47.31957437886096</v>
+        <v>-45.83256067272502</v>
       </c>
       <c r="F100">
-        <v>-2.324105009074927</v>
+        <v>-0.3063130170873061</v>
       </c>
       <c r="G100">
-        <v>-12.17554103179539</v>
+        <v>-12.14045262449083</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.3349293359637</v>
       </c>
       <c r="E101">
-        <v>-49.08218999699838</v>
+        <v>-48.84527628679052</v>
       </c>
       <c r="F101">
-        <v>-2.860701531790779</v>
+        <v>-0.505610758894242</v>
       </c>
       <c r="G101">
-        <v>-12.88365720335993</v>
+        <v>-11.50104863981979</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.4605079838778</v>
       </c>
       <c r="E102">
-        <v>-51.05030028167132</v>
+        <v>-51.14310378872462</v>
       </c>
       <c r="F102">
-        <v>-3.345766146745877</v>
+        <v>-0.8601271562703464</v>
       </c>
       <c r="G102">
-        <v>-13.68115091062894</v>
+        <v>-12.2103801129915</v>
       </c>
     </row>
   </sheetData>
